--- a/data/trans_orig/P23_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P23_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2007</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88381</t>
+          <t>87907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121418</t>
+          <t>119139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51223</t>
+          <t>50942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80841</t>
+          <t>80075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147792</t>
+          <t>147347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190904</t>
+          <t>190893</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151592</t>
+          <t>153871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184629</t>
+          <t>185103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179997</t>
+          <t>180763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>209615</t>
+          <t>209896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>342944</t>
+          <t>342955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>386056</t>
+          <t>386501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>154935</t>
+          <t>155028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>198022</t>
+          <t>199077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>93952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>132951</t>
+          <t>131694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258740</t>
+          <t>260527</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>317840</t>
+          <t>317720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>294011</t>
+          <t>292956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>337098</t>
+          <t>337005</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370998</t>
+          <t>372255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>407574</t>
+          <t>409997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678142</t>
+          <t>678262</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>737242</t>
+          <t>735455</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120687</t>
+          <t>117184</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155868</t>
+          <t>153800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79385</t>
+          <t>78280</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111539</t>
+          <t>110217</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207202</t>
+          <t>207027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255426</t>
+          <t>255813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>162978</t>
+          <t>165046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198159</t>
+          <t>201662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>223873</t>
+          <t>225195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256027</t>
+          <t>257132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>398832</t>
+          <t>398445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>447056</t>
+          <t>447231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143632</t>
+          <t>143928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>182401</t>
+          <t>180536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82584</t>
+          <t>82288</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115588</t>
+          <t>115301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>235453</t>
+          <t>233758</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>286978</t>
+          <t>286602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176270</t>
+          <t>178135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215039</t>
+          <t>214743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255868</t>
+          <t>256155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288872</t>
+          <t>289168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>443149</t>
+          <t>443525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>494674</t>
+          <t>496369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64570</t>
+          <t>64267</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93419</t>
+          <t>93207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44235</t>
+          <t>44772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70451</t>
+          <t>70689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116220</t>
+          <t>116772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155337</t>
+          <t>155087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109889</t>
+          <t>110101</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138738</t>
+          <t>139041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137217</t>
+          <t>136979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163433</t>
+          <t>162896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255639</t>
+          <t>255889</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>294756</t>
+          <t>294204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,59%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>108012</t>
+          <t>107432</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>141423</t>
+          <t>138636</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51015</t>
+          <t>50947</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78067</t>
+          <t>78818</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>166413</t>
+          <t>165796</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209564</t>
+          <t>209249</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129388</t>
+          <t>132175</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162799</t>
+          <t>163379</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>200077</t>
+          <t>199326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227129</t>
+          <t>227197</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>339391</t>
+          <t>339706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>382542</t>
+          <t>383159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>204518</t>
+          <t>203434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>251896</t>
+          <t>254575</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139384</t>
+          <t>139565</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181712</t>
+          <t>183821</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>355484</t>
+          <t>355020</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>420527</t>
+          <t>423257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>363131</t>
+          <t>360452</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>410509</t>
+          <t>411593</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>456507</t>
+          <t>454398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>498835</t>
+          <t>498654</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>832719</t>
+          <t>829989</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>897762</t>
+          <t>898226</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>271394</t>
+          <t>270803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>322418</t>
+          <t>322911</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154791</t>
+          <t>156200</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203734</t>
+          <t>203531</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>440606</t>
+          <t>440119</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>511718</t>
+          <t>511993</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>421377</t>
+          <t>420884</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>472401</t>
+          <t>472992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>579777</t>
+          <t>579980</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>628720</t>
+          <t>627311</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1015588</t>
+          <t>1015313</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1086700</t>
+          <t>1087187</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1244842</t>
+          <t>1252736</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1361477</t>
+          <t>1365380</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>785050</t>
+          <t>781070</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>885840</t>
+          <t>876985</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2055957</t>
+          <t>2058038</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2216426</t>
+          <t>2217789</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1914024</t>
+          <t>1910121</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2030659</t>
+          <t>2022765</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2493357</t>
+          <t>2502212</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2594147</t>
+          <t>2598127</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4438272</t>
+          <t>4436909</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4598741</t>
+          <t>4596660</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2012</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97012</t>
+          <t>96690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132861</t>
+          <t>130505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80428</t>
+          <t>80556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116333</t>
+          <t>113738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>187388</t>
+          <t>186289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>238150</t>
+          <t>235848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161877</t>
+          <t>164233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197726</t>
+          <t>198048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170912</t>
+          <t>173507</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>206817</t>
+          <t>206689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343833</t>
+          <t>346135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>394595</t>
+          <t>395694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178781</t>
+          <t>174470</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>222752</t>
+          <t>223069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>124331</t>
+          <t>125472</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169100</t>
+          <t>168456</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>315028</t>
+          <t>313924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379994</t>
+          <t>374922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282775</t>
+          <t>282458</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>326746</t>
+          <t>331057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354665</t>
+          <t>355309</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>399434</t>
+          <t>398293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>649298</t>
+          <t>654370</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714264</t>
+          <t>715368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108240</t>
+          <t>108827</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143519</t>
+          <t>145311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71428</t>
+          <t>71149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104818</t>
+          <t>104397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186318</t>
+          <t>187291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236197</t>
+          <t>236096</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>180527</t>
+          <t>178735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215806</t>
+          <t>215219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235216</t>
+          <t>235637</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>268606</t>
+          <t>268885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>427883</t>
+          <t>427984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>477762</t>
+          <t>476789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,8%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97606</t>
+          <t>101062</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136539</t>
+          <t>137540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84980</t>
+          <t>85416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121095</t>
+          <t>120556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>195320</t>
+          <t>195505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>245185</t>
+          <t>247175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237443</t>
+          <t>236442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276376</t>
+          <t>272920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>267856</t>
+          <t>268395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303971</t>
+          <t>303535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>517748</t>
+          <t>515758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>567613</t>
+          <t>567428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73480</t>
+          <t>73177</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104750</t>
+          <t>103060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52121</t>
+          <t>52235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80921</t>
+          <t>79231</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>135987</t>
+          <t>133847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>177734</t>
+          <t>173258</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107868</t>
+          <t>109558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139138</t>
+          <t>139441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138670</t>
+          <t>140360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167470</t>
+          <t>167356</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254475</t>
+          <t>258951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>296222</t>
+          <t>298362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68317</t>
+          <t>67328</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99884</t>
+          <t>98536</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53888</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82745</t>
+          <t>82596</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129923</t>
+          <t>128975</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169935</t>
+          <t>171683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174097</t>
+          <t>175445</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>205664</t>
+          <t>206653</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197286</t>
+          <t>197435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226143</t>
+          <t>225885</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>384077</t>
+          <t>382329</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>424089</t>
+          <t>425037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>230841</t>
+          <t>228346</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>281727</t>
+          <t>281443</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>166240</t>
+          <t>166666</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>216745</t>
+          <t>214942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>412483</t>
+          <t>408176</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>485830</t>
+          <t>480943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>381061</t>
+          <t>381345</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>431947</t>
+          <t>434442</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>477108</t>
+          <t>478911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>527613</t>
+          <t>527187</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>870811</t>
+          <t>875698</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>944158</t>
+          <t>948465</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>251617</t>
+          <t>252833</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>306187</t>
+          <t>307871</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183752</t>
+          <t>186515</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>234855</t>
+          <t>235881</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>450066</t>
+          <t>448823</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>525310</t>
+          <t>523927</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>471882</t>
+          <t>470198</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>526452</t>
+          <t>525236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>588002</t>
+          <t>586976</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>639105</t>
+          <t>636342</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1075616</t>
+          <t>1076999</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1150860</t>
+          <t>1152103</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,96%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1206177</t>
+          <t>1203028</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1328041</t>
+          <t>1319774</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>902400</t>
+          <t>905512</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1013655</t>
+          <t>1012153</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2136501</t>
+          <t>2142650</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2303716</t>
+          <t>2302854</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2097708</t>
+          <t>2105975</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2219572</t>
+          <t>2222721</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2542672</t>
+          <t>2544174</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2653927</t>
+          <t>2650815</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4678360</t>
+          <t>4679222</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4845575</t>
+          <t>4839426</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2016</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87879</t>
+          <t>90606</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122585</t>
+          <t>124241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60864</t>
+          <t>60767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91416</t>
+          <t>88898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>157201</t>
+          <t>158516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>202125</t>
+          <t>204488</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171176</t>
+          <t>169520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>205882</t>
+          <t>203155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197287</t>
+          <t>199805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227839</t>
+          <t>227936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>380339</t>
+          <t>377976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425263</t>
+          <t>423948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>187173</t>
+          <t>183921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>232909</t>
+          <t>230535</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120089</t>
+          <t>120289</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164421</t>
+          <t>163533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319532</t>
+          <t>319574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>384295</t>
+          <t>379528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>268802</t>
+          <t>271176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314538</t>
+          <t>317790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356465</t>
+          <t>357353</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>400797</t>
+          <t>400597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>638302</t>
+          <t>643069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>703065</t>
+          <t>703023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80584</t>
+          <t>81827</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111956</t>
+          <t>113817</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67302</t>
+          <t>66983</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98919</t>
+          <t>98032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155752</t>
+          <t>157093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199656</t>
+          <t>201232</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206609</t>
+          <t>204748</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237981</t>
+          <t>236738</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>237390</t>
+          <t>238277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269007</t>
+          <t>269326</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>455218</t>
+          <t>453642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>499122</t>
+          <t>497781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>122442</t>
+          <t>121648</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161134</t>
+          <t>160332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>91976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128282</t>
+          <t>127693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222348</t>
+          <t>220847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275071</t>
+          <t>275846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>208830</t>
+          <t>209632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>247522</t>
+          <t>248316</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257716</t>
+          <t>258305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>295930</t>
+          <t>294022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>480891</t>
+          <t>480116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>533614</t>
+          <t>535115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71402</t>
+          <t>70591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101117</t>
+          <t>99059</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>44876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70679</t>
+          <t>69422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123408</t>
+          <t>122806</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162402</t>
+          <t>162112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110104</t>
+          <t>112162</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139819</t>
+          <t>140630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>147908</t>
+          <t>149165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173542</t>
+          <t>173711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267406</t>
+          <t>267696</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306400</t>
+          <t>307002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,43%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73211</t>
+          <t>74527</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>104354</t>
+          <t>105077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58397</t>
+          <t>59102</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87098</t>
+          <t>89195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141283</t>
+          <t>141288</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>182249</t>
+          <t>181631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158769</t>
+          <t>158046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>189912</t>
+          <t>188596</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186017</t>
+          <t>183920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214718</t>
+          <t>214013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>353989</t>
+          <t>354607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>394955</t>
+          <t>394950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172859</t>
+          <t>173584</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>221375</t>
+          <t>222023</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149358</t>
+          <t>150282</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197776</t>
+          <t>197829</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>336975</t>
+          <t>337941</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>404221</t>
+          <t>403176</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>434111</t>
+          <t>433463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>482627</t>
+          <t>481902</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>491563</t>
+          <t>491510</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>539981</t>
+          <t>539057</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>940604</t>
+          <t>941649</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1007850</t>
+          <t>1006884</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,87%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>229046</t>
+          <t>227767</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>285657</t>
+          <t>282897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>189432</t>
+          <t>189123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241509</t>
+          <t>239010</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>435702</t>
+          <t>432566</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>510983</t>
+          <t>506228</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>492926</t>
+          <t>495686</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>549537</t>
+          <t>550816</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>584658</t>
+          <t>587157</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>636735</t>
+          <t>637044</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1093767</t>
+          <t>1098522</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1169048</t>
+          <t>1172184</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1119083</t>
+          <t>1118666</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1234664</t>
+          <t>1233119</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>870508</t>
+          <t>869521</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>975209</t>
+          <t>974405</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2015020</t>
+          <t>2015671</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2174439</t>
+          <t>2174376</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2157750</t>
+          <t>2159295</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2273331</t>
+          <t>2273748</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2563894</t>
+          <t>2564698</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2668595</t>
+          <t>2669582</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4757078</t>
+          <t>4757141</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4916497</t>
+          <t>4915846</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2023</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67208</t>
+          <t>66034</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106245</t>
+          <t>103323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54768</t>
+          <t>54381</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77529</t>
+          <t>77170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128946</t>
+          <t>128251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>173328</t>
+          <t>175631</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>205198</t>
+          <t>208120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244235</t>
+          <t>245409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212106</t>
+          <t>212465</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>234867</t>
+          <t>235254</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>427749</t>
+          <t>425446</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>472131</t>
+          <t>472826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109896</t>
+          <t>110963</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>160588</t>
+          <t>165244</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84719</t>
+          <t>83493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>116780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201630</t>
+          <t>204287</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>261580</t>
+          <t>266833</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357802</t>
+          <t>353146</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408494</t>
+          <t>407427</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>397810</t>
+          <t>398189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>430250</t>
+          <t>431476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771779</t>
+          <t>766526</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>831729</t>
+          <t>829072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61003</t>
+          <t>59875</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90465</t>
+          <t>88508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53317</t>
+          <t>52181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77451</t>
+          <t>77235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121274</t>
+          <t>120589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157059</t>
+          <t>158363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>225585</t>
+          <t>227542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>255047</t>
+          <t>256175</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271677</t>
+          <t>271893</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>295811</t>
+          <t>296947</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>508119</t>
+          <t>506815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543904</t>
+          <t>544589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58427</t>
+          <t>58406</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97959</t>
+          <t>97273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>43776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98698</t>
+          <t>97946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108253</t>
+          <t>107978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183309</t>
+          <t>181652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214598</t>
+          <t>215284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>254130</t>
+          <t>254151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>377020</t>
+          <t>377772</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>431067</t>
+          <t>431942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>604965</t>
+          <t>606622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>680021</t>
+          <t>680296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26542</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>43348</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37153</t>
+          <t>37201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52613</t>
+          <t>53280</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75048</t>
+          <t>76239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135284</t>
+          <t>135394</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152200</t>
+          <t>152336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171503</t>
+          <t>171455</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>184420</t>
+          <t>185147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312350</t>
+          <t>311159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>334785</t>
+          <t>334118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62371</t>
+          <t>61342</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89222</t>
+          <t>88719</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38682</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58521</t>
+          <t>59256</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106411</t>
+          <t>106662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139515</t>
+          <t>140288</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180414</t>
+          <t>180917</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207265</t>
+          <t>208294</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>198535</t>
+          <t>197800</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>218374</t>
+          <t>218544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>387177</t>
+          <t>386404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>420281</t>
+          <t>420030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145050</t>
+          <t>146879</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205504</t>
+          <t>202886</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62261</t>
+          <t>73877</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211564</t>
+          <t>209868</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>199352</t>
+          <t>204385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390634</t>
+          <t>392400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>417581</t>
+          <t>420199</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>478035</t>
+          <t>476206</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>633795</t>
+          <t>635491</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>783098</t>
+          <t>771482</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1077810</t>
+          <t>1076044</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1269092</t>
+          <t>1264059</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82444</t>
+          <t>82620</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>259735</t>
+          <t>260226</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>102976</t>
+          <t>103927</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137799</t>
+          <t>137918</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>189365</t>
+          <t>183972</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>364962</t>
+          <t>365813</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>667982</t>
+          <t>667491</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>845273</t>
+          <t>845097</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>579932</t>
+          <t>579813</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>614755</t>
+          <t>613804</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1280487</t>
+          <t>1279636</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1456084</t>
+          <t>1461477</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>665502</t>
+          <t>659122</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>926490</t>
+          <t>919495</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>525297</t>
+          <t>541235</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>713537</t>
+          <t>718797</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1287875</t>
+          <t>1274431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1605712</t>
+          <t>1605487</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2531130</t>
+          <t>2538125</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2792118</t>
+          <t>2798498</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2944714</t>
+          <t>2939454</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3132954</t>
+          <t>3117016</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5510159</t>
+          <t>5510384</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5827996</t>
+          <t>5841440</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P23_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87907</t>
+          <t>85271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119139</t>
+          <t>119582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50942</t>
+          <t>51420</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80075</t>
+          <t>80356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>147347</t>
+          <t>147095</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190893</t>
+          <t>190519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153871</t>
+          <t>153428</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>185103</t>
+          <t>187739</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180763</t>
+          <t>180482</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>209896</t>
+          <t>209418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>342955</t>
+          <t>343329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>386501</t>
+          <t>386753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,45%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>155028</t>
+          <t>153771</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>199077</t>
+          <t>200389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93952</t>
+          <t>95207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131694</t>
+          <t>132819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260527</t>
+          <t>263305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>317720</t>
+          <t>320679</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>292956</t>
+          <t>291644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>337005</t>
+          <t>338262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372255</t>
+          <t>371130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>409997</t>
+          <t>408742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678262</t>
+          <t>675303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735455</t>
+          <t>732677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117184</t>
+          <t>118433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153800</t>
+          <t>153290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78280</t>
+          <t>77800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110217</t>
+          <t>111337</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207027</t>
+          <t>207149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255813</t>
+          <t>254505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165046</t>
+          <t>165556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201662</t>
+          <t>200413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>225195</t>
+          <t>224075</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257132</t>
+          <t>257612</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>398445</t>
+          <t>399753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>447231</t>
+          <t>447109</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143928</t>
+          <t>143869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180536</t>
+          <t>178776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82288</t>
+          <t>82815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115301</t>
+          <t>113786</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>233758</t>
+          <t>234817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>286602</t>
+          <t>284495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178135</t>
+          <t>179895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>214743</t>
+          <t>214802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256155</t>
+          <t>257670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>289168</t>
+          <t>288641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>443525</t>
+          <t>445632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>496369</t>
+          <t>495310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,84%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64267</t>
+          <t>65523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93207</t>
+          <t>92890</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44772</t>
+          <t>44331</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70689</t>
+          <t>71968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116772</t>
+          <t>115847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155087</t>
+          <t>154568</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>110418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139041</t>
+          <t>137785</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136979</t>
+          <t>135700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162896</t>
+          <t>163337</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255889</t>
+          <t>256408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>294204</t>
+          <t>295129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107432</t>
+          <t>108253</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>138636</t>
+          <t>138909</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50947</t>
+          <t>50553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78818</t>
+          <t>76720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>165796</t>
+          <t>165235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209249</t>
+          <t>208080</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132175</t>
+          <t>131902</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>163379</t>
+          <t>162558</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>199326</t>
+          <t>201424</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227197</t>
+          <t>227591</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>339706</t>
+          <t>340875</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>383159</t>
+          <t>383720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>203434</t>
+          <t>204306</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>254575</t>
+          <t>252082</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139565</t>
+          <t>139459</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>183821</t>
+          <t>184869</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>355020</t>
+          <t>358430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>423257</t>
+          <t>423298</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>360452</t>
+          <t>362945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>411593</t>
+          <t>410721</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>454398</t>
+          <t>453350</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>498654</t>
+          <t>498760</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>829989</t>
+          <t>829948</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>898226</t>
+          <t>894816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>270803</t>
+          <t>271800</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>322911</t>
+          <t>324717</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156200</t>
+          <t>154866</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>203531</t>
+          <t>202128</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>440119</t>
+          <t>437980</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>511993</t>
+          <t>510298</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>420884</t>
+          <t>419078</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>472992</t>
+          <t>471995</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>579980</t>
+          <t>581383</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>627311</t>
+          <t>628645</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1015313</t>
+          <t>1017008</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1087187</t>
+          <t>1089326</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,32%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1252736</t>
+          <t>1249910</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1365380</t>
+          <t>1361442</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>781070</t>
+          <t>782094</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>876985</t>
+          <t>883362</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2058038</t>
+          <t>2061715</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2217789</t>
+          <t>2208510</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1910121</t>
+          <t>1914059</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2022765</t>
+          <t>2025591</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2502212</t>
+          <t>2495835</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2598127</t>
+          <t>2597103</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4436909</t>
+          <t>4446188</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4596660</t>
+          <t>4592983</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96690</t>
+          <t>97820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130505</t>
+          <t>132066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80556</t>
+          <t>78871</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113738</t>
+          <t>114663</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>186289</t>
+          <t>186941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235848</t>
+          <t>234753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>164233</t>
+          <t>162672</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>198048</t>
+          <t>196918</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173507</t>
+          <t>172582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>206689</t>
+          <t>208374</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346135</t>
+          <t>347230</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>395694</t>
+          <t>395042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>174470</t>
+          <t>180061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223069</t>
+          <t>226806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125472</t>
+          <t>125344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168456</t>
+          <t>165806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>313924</t>
+          <t>307396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>374922</t>
+          <t>373416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282458</t>
+          <t>278721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>331057</t>
+          <t>325466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355309</t>
+          <t>357959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>398293</t>
+          <t>398421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>654370</t>
+          <t>655876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>715368</t>
+          <t>721896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>70,14%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108827</t>
+          <t>107589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145311</t>
+          <t>143134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71149</t>
+          <t>68517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104397</t>
+          <t>102405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187291</t>
+          <t>185541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236096</t>
+          <t>236858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178735</t>
+          <t>180912</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215219</t>
+          <t>216457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235637</t>
+          <t>237629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>268885</t>
+          <t>271517</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>427984</t>
+          <t>427222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>476789</t>
+          <t>478539</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101062</t>
+          <t>98961</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137540</t>
+          <t>135736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85416</t>
+          <t>85219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120556</t>
+          <t>121554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>195505</t>
+          <t>193624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>247175</t>
+          <t>244606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236442</t>
+          <t>238246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272920</t>
+          <t>275021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>268395</t>
+          <t>267397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>303732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>515758</t>
+          <t>518327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>567428</t>
+          <t>569309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,62%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73177</t>
+          <t>72957</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103060</t>
+          <t>104416</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52235</t>
+          <t>52304</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79231</t>
+          <t>79572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133847</t>
+          <t>132509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173258</t>
+          <t>175435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109558</t>
+          <t>108202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139441</t>
+          <t>139661</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140360</t>
+          <t>140019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167356</t>
+          <t>167287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258951</t>
+          <t>256774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>298362</t>
+          <t>299700</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67328</t>
+          <t>67233</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98536</t>
+          <t>98393</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>53824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82596</t>
+          <t>80585</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128975</t>
+          <t>128324</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>171683</t>
+          <t>170375</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175445</t>
+          <t>175588</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206653</t>
+          <t>206748</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197435</t>
+          <t>199446</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225885</t>
+          <t>226207</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>382329</t>
+          <t>383637</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>425037</t>
+          <t>425688</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228346</t>
+          <t>233402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>281443</t>
+          <t>284822</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>166666</t>
+          <t>166565</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>214942</t>
+          <t>215055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>408176</t>
+          <t>411141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>480943</t>
+          <t>484492</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>381345</t>
+          <t>377966</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>434442</t>
+          <t>429386</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>478911</t>
+          <t>478798</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>527187</t>
+          <t>527288</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>875698</t>
+          <t>872149</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>948465</t>
+          <t>945500</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>252833</t>
+          <t>251816</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>307871</t>
+          <t>306917</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>186515</t>
+          <t>180784</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>235881</t>
+          <t>235513</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>448823</t>
+          <t>449618</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>523927</t>
+          <t>528609</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>470198</t>
+          <t>471152</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>525236</t>
+          <t>526253</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>586976</t>
+          <t>587344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>636342</t>
+          <t>642073</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1076999</t>
+          <t>1072317</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1152103</t>
+          <t>1151308</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1203028</t>
+          <t>1207570</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1319774</t>
+          <t>1324861</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>905512</t>
+          <t>901501</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1012153</t>
+          <t>1014393</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2142650</t>
+          <t>2140869</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2302854</t>
+          <t>2304193</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2105975</t>
+          <t>2100888</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2222721</t>
+          <t>2218179</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2544174</t>
+          <t>2541934</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2650815</t>
+          <t>2654826</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4679222</t>
+          <t>4677883</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4839426</t>
+          <t>4841207</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90606</t>
+          <t>91302</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124241</t>
+          <t>125716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60767</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88898</t>
+          <t>89324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158516</t>
+          <t>159379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>204488</t>
+          <t>204249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169520</t>
+          <t>168045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203155</t>
+          <t>202459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199805</t>
+          <t>199379</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>227936</t>
+          <t>229382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>377976</t>
+          <t>378215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>423948</t>
+          <t>423085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183921</t>
+          <t>188166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230535</t>
+          <t>232082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120289</t>
+          <t>121769</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>163533</t>
+          <t>161616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319574</t>
+          <t>318730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379528</t>
+          <t>380696</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271176</t>
+          <t>269629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>317790</t>
+          <t>313545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>357353</t>
+          <t>359270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>400597</t>
+          <t>399117</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643069</t>
+          <t>641901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>703023</t>
+          <t>703867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,83%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81827</t>
+          <t>80774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113817</t>
+          <t>111823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66983</t>
+          <t>66327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98032</t>
+          <t>98166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157093</t>
+          <t>155501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201232</t>
+          <t>200650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>204748</t>
+          <t>206742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>236738</t>
+          <t>237791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>238277</t>
+          <t>238143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269326</t>
+          <t>269982</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>453642</t>
+          <t>454224</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>497781</t>
+          <t>499373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121648</t>
+          <t>121819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160332</t>
+          <t>158063</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91976</t>
+          <t>91997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127693</t>
+          <t>128018</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>220847</t>
+          <t>221039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275846</t>
+          <t>274216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>209632</t>
+          <t>211901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>248316</t>
+          <t>248145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258305</t>
+          <t>257980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294022</t>
+          <t>294001</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>480116</t>
+          <t>481746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>535115</t>
+          <t>534923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70591</t>
+          <t>71232</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99059</t>
+          <t>98543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44876</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69422</t>
+          <t>70083</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122806</t>
+          <t>123780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162112</t>
+          <t>160824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112162</t>
+          <t>112678</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140630</t>
+          <t>139989</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149165</t>
+          <t>148504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173711</t>
+          <t>172558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267696</t>
+          <t>268984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>307002</t>
+          <t>306028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74527</t>
+          <t>72465</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105077</t>
+          <t>102633</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59102</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89195</t>
+          <t>88668</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141288</t>
+          <t>140216</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>181631</t>
+          <t>183749</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158046</t>
+          <t>160490</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188596</t>
+          <t>190658</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183920</t>
+          <t>184447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>214013</t>
+          <t>214474</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>354607</t>
+          <t>352489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>394950</t>
+          <t>396022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,85%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173584</t>
+          <t>171880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222023</t>
+          <t>220793</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150282</t>
+          <t>150747</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197829</t>
+          <t>195895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>337941</t>
+          <t>338494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>403176</t>
+          <t>406004</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,19%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>433463</t>
+          <t>434693</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>481902</t>
+          <t>483606</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>491510</t>
+          <t>493444</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>539057</t>
+          <t>538592</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>941649</t>
+          <t>938821</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1006884</t>
+          <t>1006331</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>227767</t>
+          <t>229580</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>282897</t>
+          <t>284093</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,82 +9795,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>29,49%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>36,49%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>214288</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>189186</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>243262</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>25,94%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>22,9%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>469347</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>433127</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>510548</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>29,25%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>36,33%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>214288</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>189123</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>239010</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>22,89%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>28,93%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>469347</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>432566</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>506228</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>495686</t>
+          <t>494490</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>550816</t>
+          <t>549003</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,82 +9908,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>70,51%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>611879</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>582905</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>636981</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>74,06%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>70,56%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>77,1%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1135403</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1094202</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1171623</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>70,75%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>611879</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>587157</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>637044</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>74,06%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>71,07%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>77,11%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1135403</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1098522</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1172184</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>70,75%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1118666</t>
+          <t>1127117</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1233119</t>
+          <t>1237940</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>869521</t>
+          <t>869748</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>974405</t>
+          <t>982473</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2015671</t>
+          <t>2019716</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2174376</t>
+          <t>2177719</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2159295</t>
+          <t>2154474</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2273748</t>
+          <t>2265297</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2564698</t>
+          <t>2556630</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2669582</t>
+          <t>2669355</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4757141</t>
+          <t>4753798</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4915846</t>
+          <t>4911801</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84344</t>
+          <t>75950</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66034</t>
+          <t>61060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103323</t>
+          <t>92437</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>66333</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54381</t>
+          <t>56641</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77170</t>
+          <t>78816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>149375</t>
+          <t>142284</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128251</t>
+          <t>122328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175631</t>
+          <t>161684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>227099</t>
+          <t>242895</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>208120</t>
+          <t>226408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245409</t>
+          <t>257785</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>224604</t>
+          <t>249728</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>212465</t>
+          <t>237245</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235254</t>
+          <t>259420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>451702</t>
+          <t>492622</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>425446</t>
+          <t>473222</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>472826</t>
+          <t>512578</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>133670</t>
+          <t>136735</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110963</t>
+          <t>110841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>165244</t>
+          <t>164787</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>99807</t>
+          <t>103279</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83493</t>
+          <t>87384</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116780</t>
+          <t>121322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>233477</t>
+          <t>240014</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204287</t>
+          <t>210228</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>266833</t>
+          <t>271827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>384720</t>
+          <t>393912</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353146</t>
+          <t>365860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407427</t>
+          <t>419806</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>415162</t>
+          <t>443215</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>398189</t>
+          <t>425172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>431476</t>
+          <t>459110</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>799882</t>
+          <t>837127</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>766526</t>
+          <t>805314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>829072</t>
+          <t>866913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74218</t>
+          <t>79561</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59875</t>
+          <t>64901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88508</t>
+          <t>95825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>64222</t>
+          <t>64635</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52181</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77235</t>
+          <t>76532</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>138439</t>
+          <t>144196</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120589</t>
+          <t>126262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158363</t>
+          <t>165136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>241832</t>
+          <t>236432</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227542</t>
+          <t>220168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>256175</t>
+          <t>251092</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>284906</t>
+          <t>291746</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>271893</t>
+          <t>279849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>296947</t>
+          <t>303802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>526739</t>
+          <t>528179</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>506815</t>
+          <t>507239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>544589</t>
+          <t>546113</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>76597</t>
+          <t>92572</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58406</t>
+          <t>70901</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97273</t>
+          <t>117416</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>73571</t>
+          <t>80223</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43776</t>
+          <t>64784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97946</t>
+          <t>99381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>150168</t>
+          <t>172796</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107978</t>
+          <t>145649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181652</t>
+          <t>202841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>235960</t>
+          <t>280573</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215284</t>
+          <t>255729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>254151</t>
+          <t>302244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>402147</t>
+          <t>341738</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>377772</t>
+          <t>322580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>431942</t>
+          <t>357177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>638106</t>
+          <t>622311</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>606622</t>
+          <t>592266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>680296</t>
+          <t>649458</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26406</t>
+          <t>31912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43348</t>
+          <t>51507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23509</t>
+          <t>24782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>40849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>63622</t>
+          <t>73293</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53280</t>
+          <t>62002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76239</t>
+          <t>85604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>144976</t>
+          <t>164544</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135394</t>
+          <t>154158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152336</t>
+          <t>173753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>178800</t>
+          <t>195043</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171455</t>
+          <t>186366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185147</t>
+          <t>202433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>323776</t>
+          <t>359586</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>311159</t>
+          <t>347275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>334118</t>
+          <t>370877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>75056</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61342</t>
+          <t>62929</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88719</t>
+          <t>90755</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48078</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59256</t>
+          <t>59647</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>123134</t>
+          <t>124861</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106662</t>
+          <t>107953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>140288</t>
+          <t>142137</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>194580</t>
+          <t>194732</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180917</t>
+          <t>179952</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208294</t>
+          <t>207778</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>208978</t>
+          <t>214864</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197800</t>
+          <t>204103</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>218544</t>
+          <t>223870</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>403558</t>
+          <t>409596</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>386404</t>
+          <t>392320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>420030</t>
+          <t>426504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>173018</t>
+          <t>190195</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146879</t>
+          <t>162403</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>202886</t>
+          <t>216800</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>152222</t>
+          <t>176378</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73877</t>
+          <t>154916</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209868</t>
+          <t>199377</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>325240</t>
+          <t>366573</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>204385</t>
+          <t>334030</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>392400</t>
+          <t>403660</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>450067</t>
+          <t>527232</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>420199</t>
+          <t>500627</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>476206</t>
+          <t>555024</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>693137</t>
+          <t>591807</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>635491</t>
+          <t>568808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>771482</t>
+          <t>613269</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1143204</t>
+          <t>1119039</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1076044</t>
+          <t>1081952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1264059</t>
+          <t>1151582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623085</t>
+          <t>717427</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623085</t>
+          <t>717427</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623085</t>
+          <t>717427</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>845359</t>
+          <t>768185</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>845359</t>
+          <t>768185</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>845359</t>
+          <t>768185</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1468444</t>
+          <t>1485612</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1468444</t>
+          <t>1485612</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1468444</t>
+          <t>1485612</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>183841</t>
+          <t>209638</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82620</t>
+          <t>181630</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>260226</t>
+          <t>235445</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>119160</t>
+          <t>135308</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103927</t>
+          <t>114978</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137918</t>
+          <t>155198</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>303001</t>
+          <t>344946</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>183972</t>
+          <t>314624</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>365813</t>
+          <t>381992</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>743876</t>
+          <t>587292</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>667491</t>
+          <t>561485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>845097</t>
+          <t>615300</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>598571</t>
+          <t>696023</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>579813</t>
+          <t>676133</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>613804</t>
+          <t>716353</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1342448</t>
+          <t>1283316</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1279636</t>
+          <t>1246270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1461477</t>
+          <t>1313638</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1645449</t>
+          <t>1628262</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1645449</t>
+          <t>1628262</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1645449</t>
+          <t>1628262</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>834510</t>
+          <t>901748</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>659122</t>
+          <t>847849</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>919495</t>
+          <t>964672</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>651946</t>
+          <t>707214</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>541235</t>
+          <t>666059</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>718797</t>
+          <t>753555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1486457</t>
+          <t>1608962</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1274431</t>
+          <t>1528923</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1605487</t>
+          <t>1683254</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2623110</t>
+          <t>2627613</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2538125</t>
+          <t>2564689</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2798498</t>
+          <t>2681512</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3006305</t>
+          <t>3024166</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2939454</t>
+          <t>2977825</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3117016</t>
+          <t>3065321</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5629414</t>
+          <t>5651778</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5510384</t>
+          <t>5577486</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5841440</t>
+          <t>5731817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
